--- a/excel/Twino.xlsx
+++ b/excel/Twino.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Twino\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.08.08\Twino\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE7E6BB-AB73-4FAC-BCBC-7749EE31EF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D4E069-6E7F-416D-AB73-9CD69145A730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Pinigai" sheetId="15" r:id="rId2"/>
-    <sheet name="8572f54e...85fb68b6201e" sheetId="24" r:id="rId3"/>
-    <sheet name="6a67a901...550919b8d681" sheetId="14" r:id="rId4"/>
+    <sheet name="LVX0000R1N56" sheetId="25" r:id="rId3"/>
+    <sheet name="LVX0000VAUM7" sheetId="24" r:id="rId4"/>
+    <sheet name="LVX0000VCV76" sheetId="14" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="48">
   <si>
     <t>Paskola</t>
   </si>
@@ -166,6 +167,24 @@
   <si>
     <t xml:space="preserve">Premijos </t>
   </si>
+  <si>
+    <t>LVX0000VCV76</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>Fincard Sp. z.o.o.</t>
+  </si>
+  <si>
+    <t>Loan (Asset Backed Securities)</t>
+  </si>
+  <si>
+    <t>LVX0000VAUM7</t>
+  </si>
+  <si>
+    <t>LVX0000R1N56</t>
+  </si>
 </sst>
 </file>
 
@@ -175,7 +194,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\.mm\.dd;@"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -207,6 +226,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF181D27"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -328,7 +353,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -407,6 +432,9 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -439,7 +467,35 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="15">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -551,6 +607,62 @@
           <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09AAB2CB-F6D7-42C3-83F4-EA727B53D009}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F3E6BE7-2620-4CB3-8F4E-0C17BF712D36}"/>
             </a:ext>
           </a:extLst>
@@ -586,7 +698,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -911,7 +1023,8 @@
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="25.7109375" customWidth="1"/>
-    <col min="4" max="5" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
     <col min="6" max="6" width="20.7109375" customWidth="1"/>
     <col min="7" max="8" width="10.7109375" customWidth="1"/>
     <col min="9" max="10" width="12.7109375" customWidth="1"/>
@@ -922,43 +1035,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="32" t="s">
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="37" t="s">
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="Q1" s="38" t="s">
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="Q1" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="40"/>
-      <c r="U1" s="38" t="s">
+      <c r="R1" s="40"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="V1" s="40"/>
-      <c r="W1" s="32" t="s">
+      <c r="V1" s="41"/>
+      <c r="W1" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
       <c r="AA1" s="4" t="s">
         <v>25</v>
       </c>
@@ -1052,69 +1165,69 @@
         <v>1</v>
       </c>
       <c r="B3" s="6">
-        <f>'8572f54e...85fb68b6201e'!B9</f>
-        <v>0</v>
-      </c>
-      <c r="C3" s="26">
-        <f>'6a67a901...550919b8d681'!B1</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <f>'6a67a901...550919b8d681'!B2</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <f>'6a67a901...550919b8d681'!B3</f>
-        <v>0</v>
+        <f>LVX0000VCV76!B9</f>
+        <v>46251</v>
+      </c>
+      <c r="C3" s="26" t="str">
+        <f>LVX0000VCV76!B1</f>
+        <v>LVX0000VCV76</v>
+      </c>
+      <c r="D3" s="2" t="str">
+        <f>LVX0000VCV76!B2</f>
+        <v>Poland</v>
+      </c>
+      <c r="E3" s="2" t="str">
+        <f>LVX0000VCV76!B3</f>
+        <v>Fincard Sp. z.o.o.</v>
       </c>
       <c r="F3" s="2" t="str">
-        <f>'6a67a901...550919b8d681'!B8</f>
-        <v>0 m. 0 mėn. 0 d.</v>
+        <f>LVX0000VCV76!B8</f>
+        <v>0 m. 11 mėn. 23 d.</v>
       </c>
       <c r="G3" s="7">
-        <f>'6a67a901...550919b8d681'!B15</f>
-        <v>0</v>
+        <f>LVX0000VCV76!B15</f>
+        <v>0.12</v>
       </c>
       <c r="H3" s="3">
-        <f>'6a67a901...550919b8d681'!B16</f>
-        <v>0</v>
+        <f>LVX0000VCV76!B16</f>
+        <v>10</v>
       </c>
       <c r="I3" s="6">
-        <f>'6a67a901...550919b8d681'!B11</f>
-        <v>0</v>
-      </c>
-      <c r="J3" s="6">
-        <f>'6a67a901...550919b8d681'!O3</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="19" t="str">
-        <f ca="1">'6a67a901...550919b8d681'!B12</f>
-        <v/>
+        <f>LVX0000VCV76!B11</f>
+        <v>46608</v>
+      </c>
+      <c r="J3" s="6" t="str">
+        <f>LVX0000VCV76!O3</f>
+        <v/>
+      </c>
+      <c r="K3" s="19">
+        <f ca="1">LVX0000VCV76!B12</f>
+        <v>342</v>
       </c>
       <c r="L3" s="19" t="str">
-        <f ca="1">'6a67a901...550919b8d681'!P3</f>
+        <f ca="1">LVX0000VCV76!P3</f>
         <v/>
       </c>
       <c r="M3" s="3">
-        <f>'6a67a901...550919b8d681'!K3</f>
+        <f>LVX0000VCV76!K3</f>
         <v>0</v>
       </c>
       <c r="N3" s="3">
-        <f>'6a67a901...550919b8d681'!L3</f>
+        <f>LVX0000VCV76!L3</f>
         <v>0</v>
       </c>
       <c r="O3" s="3">
-        <f>'6a67a901...550919b8d681'!M3</f>
+        <f>LVX0000VCV76!M3</f>
         <v>0</v>
       </c>
       <c r="P3" s="10"/>
       <c r="Q3" s="29">
         <f>Pinigai!I2</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R3" s="29">
         <f>SUM(H3:H93)-U3</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S3" s="30">
         <f>Pinigai!H2</f>
@@ -1122,7 +1235,7 @@
       </c>
       <c r="T3" s="29">
         <f>W3-R3</f>
-        <v>0</v>
+        <v>3.0000000000001137E-2</v>
       </c>
       <c r="U3" s="29">
         <f>SUM(M3:M93)</f>
@@ -1130,30 +1243,30 @@
       </c>
       <c r="V3" s="29">
         <f>SUM(N3:N93)-AA3</f>
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="W3" s="29">
         <f>Q3+V3+S3</f>
-        <v>0</v>
+        <v>30.03</v>
       </c>
       <c r="X3" s="29">
         <f>W3-Q3</f>
-        <v>0</v>
-      </c>
-      <c r="Y3" s="31" t="e">
+        <v>3.0000000000001137E-2</v>
+      </c>
+      <c r="Y3" s="31">
         <f>(W3-Q3)/Q3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z3" s="31" t="e">
+        <v>1.000000000000038E-3</v>
+      </c>
+      <c r="Z3" s="31">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>#NUM!</v>
+        <v>2.2494205832481386E-2</v>
       </c>
       <c r="AA3" s="29">
         <f>SUM(O3:O93)</f>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AC3" s="3" t="str">
-        <f ca="1">'6a67a901...550919b8d681'!Z3</f>
+        <f ca="1">LVX0000VCV76!Z3</f>
         <v/>
       </c>
     </row>
@@ -1162,60 +1275,60 @@
         <v>2</v>
       </c>
       <c r="B4" s="6">
-        <f>'8572f54e...85fb68b6201e'!B9</f>
-        <v>0</v>
-      </c>
-      <c r="C4" s="26">
-        <f>'8572f54e...85fb68b6201e'!B1</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <f>'8572f54e...85fb68b6201e'!B2</f>
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <f>'8572f54e...85fb68b6201e'!B3</f>
-        <v>0</v>
+        <f>LVX0000VAUM7!B9</f>
+        <v>46251</v>
+      </c>
+      <c r="C4" s="26" t="str">
+        <f>LVX0000VAUM7!B1</f>
+        <v>LVX0000VAUM7</v>
+      </c>
+      <c r="D4" s="2" t="str">
+        <f>LVX0000VAUM7!B2</f>
+        <v>Poland</v>
+      </c>
+      <c r="E4" s="2" t="str">
+        <f>LVX0000VAUM7!B3</f>
+        <v>Fincard Sp. z.o.o.</v>
       </c>
       <c r="F4" s="2" t="str">
-        <f>'8572f54e...85fb68b6201e'!B8</f>
-        <v>0 m. 0 mėn. 0 d.</v>
+        <f>LVX0000VAUM7!B8</f>
+        <v>0 m. 5 mėn. 16 d.</v>
       </c>
       <c r="G4" s="7">
-        <f>'8572f54e...85fb68b6201e'!B15</f>
-        <v>0</v>
+        <f>LVX0000VAUM7!B15</f>
+        <v>0.1</v>
       </c>
       <c r="H4" s="3">
-        <f>'8572f54e...85fb68b6201e'!B16</f>
-        <v>0</v>
+        <f>LVX0000VAUM7!B16</f>
+        <v>10</v>
       </c>
       <c r="I4" s="6">
-        <f>'8572f54e...85fb68b6201e'!B11</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="6">
-        <f>'8572f54e...85fb68b6201e'!O3</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="19" t="str">
-        <f ca="1">'8572f54e...85fb68b6201e'!B12</f>
-        <v/>
+        <f>LVX0000VAUM7!B11</f>
+        <v>46420</v>
+      </c>
+      <c r="J4" s="6" t="str">
+        <f>LVX0000VAUM7!O3</f>
+        <v/>
+      </c>
+      <c r="K4" s="19">
+        <f ca="1">LVX0000VAUM7!B12</f>
+        <v>154</v>
       </c>
       <c r="L4" s="19" t="str">
-        <f ca="1">'8572f54e...85fb68b6201e'!P3</f>
+        <f ca="1">LVX0000VAUM7!P3</f>
         <v/>
       </c>
       <c r="M4" s="3">
-        <f>'8572f54e...85fb68b6201e'!K3</f>
+        <f>LVX0000VAUM7!K3</f>
         <v>0</v>
       </c>
       <c r="N4" s="3">
-        <f>'8572f54e...85fb68b6201e'!L3</f>
-        <v>0</v>
+        <f>LVX0000VAUM7!L3</f>
+        <v>0.04</v>
       </c>
       <c r="O4" s="3">
-        <f>'8572f54e...85fb68b6201e'!M3</f>
-        <v>0</v>
+        <f>LVX0000VAUM7!M3</f>
+        <v>0.01</v>
       </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
@@ -1230,27 +1343,86 @@
       <c r="Z4" s="20"/>
       <c r="AA4" s="20"/>
       <c r="AC4" s="3" t="str">
-        <f ca="1">'8572f54e...85fb68b6201e'!Z3</f>
+        <f ca="1">LVX0000VAUM7!Z3</f>
         <v/>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="3"/>
-      <c r="AC5" s="1"/>
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6">
+        <f>LVX0000R1N56!B9</f>
+        <v>46251</v>
+      </c>
+      <c r="C5" s="26" t="str">
+        <f>LVX0000R1N56!B1</f>
+        <v>LVX0000R1N56</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <f>LVX0000R1N56!B2</f>
+        <v>Poland</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <f>LVX0000R1N56!B3</f>
+        <v>Fincard Sp. z.o.o.</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <f>LVX0000R1N56!B8</f>
+        <v>0 m. 3 mėn. 21 d.</v>
+      </c>
+      <c r="G5" s="7">
+        <f>LVX0000R1N56!B15</f>
+        <v>0.12</v>
+      </c>
+      <c r="H5" s="3">
+        <f>LVX0000R1N56!B16</f>
+        <v>10</v>
+      </c>
+      <c r="I5" s="6">
+        <f>LVX0000R1N56!B11</f>
+        <v>46364</v>
+      </c>
+      <c r="J5" s="6" t="str">
+        <f>LVX0000R1N56!O3</f>
+        <v/>
+      </c>
+      <c r="K5" s="19">
+        <f ca="1">LVX0000R1N56!B12</f>
+        <v>98</v>
+      </c>
+      <c r="L5" s="19" t="str">
+        <f ca="1">LVX0000R1N56!P3</f>
+        <v/>
+      </c>
+      <c r="M5" s="3">
+        <f>LVX0000R1N56!K3</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="3">
+        <f>LVX0000R1N56!L3</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="3">
+        <f>LVX0000R1N56!M3</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
+      <c r="AA5" s="20"/>
+      <c r="AC5" s="3" t="str">
+        <f ca="1">LVX0000R1N56!Z3</f>
+        <v/>
+      </c>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1532,21 +1704,22 @@
     <mergeCell ref="U1:V1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:O20">
-    <cfRule type="expression" dxfId="10" priority="15">
+    <cfRule type="expression" dxfId="14" priority="15">
       <formula>$AC3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="16">
+    <cfRule type="expression" dxfId="13" priority="16">
       <formula>AND($M3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC3:AC20">
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="12" priority="2">
       <formula>AND($M3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="C3" location="'6a67a901...550919b8d681'!A1" display="'6a67a901...550919b8d681'!A1" xr:uid="{87C3E6BC-C2D4-4CD6-83E2-4126641D3546}"/>
-    <hyperlink ref="C4" location="'8572f54e...85fb68b6201e'!A1" display="'8572f54e...85fb68b6201e'!A1" xr:uid="{E1A2E8FA-E90A-432F-B098-8C25480A0509}"/>
+    <hyperlink ref="C3" location="LVX0000VCV76!A1" display="LVX0000VCV76!A1" xr:uid="{87C3E6BC-C2D4-4CD6-83E2-4126641D3546}"/>
+    <hyperlink ref="C4" location="LVX0000VAUM7!A1" display="LVX0000VAUM7!A1" xr:uid="{E1A2E8FA-E90A-432F-B098-8C25480A0509}"/>
+    <hyperlink ref="C5" location="LVX0000R1N56!A1" display="LVX0000R1N56!A1" xr:uid="{2D7EBEF7-055C-4CFF-9B59-7A31AE2C2A58}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="50" orientation="landscape" r:id="rId1"/>
@@ -1596,10 +1769,10 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>46139</v>
+        <v>46249</v>
       </c>
       <c r="B2" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3">
         <v>0</v>
@@ -1609,7 +1782,7 @@
       </c>
       <c r="F2" s="3">
         <f>SUM(B2:B35)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G2" s="3">
         <f>SUM(C2:C35)</f>
@@ -1621,19 +1794,30 @@
       </c>
       <c r="I2" s="3">
         <f>F2-G2</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K2" s="3">
         <f>B2*-1</f>
-        <v>0</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="K3" s="2"/>
+      <c r="A3" s="6">
+        <v>46251</v>
+      </c>
+      <c r="B3" s="3">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3">
+        <f>B3*-1</f>
+        <v>-9</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
@@ -3010,14 +3194,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="15">
         <f ca="1">TODAY()</f>
-        <v>46247</v>
+        <v>46266</v>
       </c>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="K200" s="3">
         <f>Overview!W3</f>
-        <v>0</v>
+        <v>30.03</v>
       </c>
     </row>
   </sheetData>
@@ -3026,10 +3210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{583E60DD-D268-4B5D-B986-F933A571227C}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1003DB2E-6C81-42D7-8E68-07FF0DC0B8B7}">
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3052,36 +3233,40 @@
       <c r="A1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="D1" s="32" t="s">
+      <c r="B1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="6"/>
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="D2" s="12" t="s">
         <v>31</v>
       </c>
@@ -3136,8 +3321,12 @@
       <c r="A3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="D3" s="11"/>
+      <c r="B3" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="11">
+        <v>46273</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="19" t="str">
         <f>IF(E3&gt;0,E3-D3,"")</f>
@@ -3159,30 +3348,30 @@
         <f>I53</f>
         <v>0</v>
       </c>
-      <c r="N3" s="7" t="e">
+      <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="O3" s="6">
+        <v/>
+      </c>
+      <c r="O3" s="6" t="str">
         <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P3" s="2" t="str">
         <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
         <v/>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="2" t="str">
         <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T3" s="13"/>
       <c r="X3" s="6">
         <f>B9</f>
-        <v>0</v>
+        <v>46251</v>
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -3193,8 +3382,12 @@
       <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="D4" s="11"/>
+      <c r="B4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="11">
+        <v>46303</v>
+      </c>
       <c r="E4" s="6"/>
       <c r="F4" s="19" t="str">
         <f>IF(E4&gt;0,E4-D4,"")</f>
@@ -3216,7 +3409,9 @@
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
-      <c r="D5" s="11"/>
+      <c r="D5" s="11">
+        <v>46334</v>
+      </c>
       <c r="E5" s="6"/>
       <c r="F5" s="19" t="str">
         <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
@@ -3238,7 +3433,9 @@
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
-      <c r="D6" s="11"/>
+      <c r="D6" s="11">
+        <v>46364</v>
+      </c>
       <c r="E6" s="6"/>
       <c r="F6" s="19" t="str">
         <f t="shared" si="0"/>
@@ -3285,7 +3482,7 @@
       </c>
       <c r="B8" s="6" t="str">
         <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>0 m. 0 mėn. 0 d.</v>
+        <v>0 m. 3 mėn. 21 d.</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="6"/>
@@ -3310,7 +3507,9 @@
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="6"/>
+      <c r="B9" s="6">
+        <v>46251</v>
+      </c>
       <c r="D9" s="11"/>
       <c r="E9" s="6"/>
       <c r="F9" s="19" t="str">
@@ -3334,7 +3533,9 @@
       <c r="A10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="6"/>
+      <c r="B10" s="6">
+        <v>46001</v>
+      </c>
       <c r="D10" s="11"/>
       <c r="E10" s="6"/>
       <c r="F10" s="19" t="str">
@@ -3358,7 +3559,9 @@
       <c r="A11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="6"/>
+      <c r="B11" s="6">
+        <v>46364</v>
+      </c>
       <c r="D11" s="11"/>
       <c r="E11" s="6"/>
       <c r="F11" s="19" t="str">
@@ -3382,9 +3585,9 @@
       <c r="A12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="19" t="str">
+      <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v/>
+        <v>98</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="6"/>
@@ -3454,7 +3657,9 @@
       <c r="A15" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="7"/>
+      <c r="B15" s="7">
+        <v>0.12</v>
+      </c>
       <c r="D15" s="11"/>
       <c r="E15" s="6"/>
       <c r="F15" s="19" t="str">
@@ -3485,7 +3690,9 @@
       <c r="A16" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="3"/>
+      <c r="B16" s="3">
+        <v>10</v>
+      </c>
       <c r="D16" s="11"/>
       <c r="E16" s="6"/>
       <c r="F16" s="19" t="str">
@@ -4250,6 +4457,1299 @@
       <c r="I53" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="X1:Z1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="11" priority="1">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>$B$16=$K$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3">
+    <cfRule type="expression" dxfId="9" priority="3">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3">
+    <cfRule type="expression" dxfId="8" priority="4">
+      <formula>$Z$3="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{583E60DD-D268-4B5D-B986-F933A571227C}">
+  <dimension ref="A1:Z53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="11" max="14" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="23" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="12.7109375" style="14" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="14" customWidth="1"/>
+    <col min="26" max="26" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" s="10"/>
+      <c r="K2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="X2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z2" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="11">
+        <v>46267</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46266</v>
+      </c>
+      <c r="F3" s="19">
+        <f>IF(E3&gt;0,E3-D3,"")</f>
+        <v>-1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="J3" s="14"/>
+      <c r="K3" s="3">
+        <f>G53</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <f>H53</f>
+        <v>0.04</v>
+      </c>
+      <c r="M3" s="3">
+        <f>I53</f>
+        <v>0.01</v>
+      </c>
+      <c r="N3" s="7" t="str">
+        <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="6" t="str">
+        <f>IF(B16=K3,MAX(E:E),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="str">
+        <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
+        <v/>
+      </c>
+      <c r="T3" s="13"/>
+      <c r="X3" s="6">
+        <f>B9</f>
+        <v>46251</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>B16*-1</f>
+        <v>-10</v>
+      </c>
+      <c r="Z3" s="2" t="str">
+        <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="11">
+        <v>46297</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="19" t="str">
+        <f>IF(E4&gt;0,E4-D4,"")</f>
+        <v/>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="10"/>
+      <c r="X4" s="6">
+        <f>E3</f>
+        <v>46266</v>
+      </c>
+      <c r="Y4" s="3">
+        <f>G3+H3-I3</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="D5" s="11">
+        <v>46328</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="19" t="str">
+        <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
+        <v/>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="10"/>
+      <c r="X5" s="6">
+        <f t="shared" ref="X5:X52" si="1">E4</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3">
+        <f t="shared" ref="Y5:Y52" si="2">G4+H4-I4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="D6" s="11">
+        <v>46358</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="10"/>
+      <c r="X6" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="D7" s="11">
+        <v>46389</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="14"/>
+      <c r="X7" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
+        <v>0 m. 5 mėn. 16 d.</v>
+      </c>
+      <c r="D8" s="11">
+        <v>46420</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="10"/>
+      <c r="X8" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46251</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="14"/>
+      <c r="X9" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46238</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="14"/>
+      <c r="X10" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46420</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="14"/>
+      <c r="X11" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="19">
+        <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
+        <v>154</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="14"/>
+      <c r="X12" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="18"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="14"/>
+      <c r="N13" s="13"/>
+      <c r="X13" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="18"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="14"/>
+      <c r="X14" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="X15" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="3">
+        <v>10</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="14"/>
+      <c r="X16" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D17" s="11"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="14"/>
+      <c r="X17" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D18" s="11"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="14"/>
+      <c r="X18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D19" s="11"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="14"/>
+      <c r="X19" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D20" s="11"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="14"/>
+      <c r="X20" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B21" s="23"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="14"/>
+      <c r="X21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D22" s="11"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="14"/>
+      <c r="X22" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D23" s="11"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="14"/>
+      <c r="X23" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D24" s="11"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="14"/>
+      <c r="X24" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D25" s="11"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="14"/>
+      <c r="X25" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D26" s="11"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="14"/>
+      <c r="X26" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D27" s="11"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="14"/>
+      <c r="X27" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D28" s="11"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="14"/>
+      <c r="X28" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D29" s="11"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="14"/>
+      <c r="X29" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D30" s="11"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="14"/>
+      <c r="X30" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D31" s="11"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="14"/>
+      <c r="X31" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D32" s="11"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="14"/>
+      <c r="X32" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D33" s="11"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="14"/>
+      <c r="X33" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D34" s="11"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="14"/>
+      <c r="X34" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="11"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="14"/>
+      <c r="X35" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="11"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="14"/>
+      <c r="X36" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D37" s="11"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="14"/>
+      <c r="X37" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D38" s="11"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="14"/>
+      <c r="X38" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="11"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="14"/>
+      <c r="X39" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="11"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="14"/>
+      <c r="X40" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D41" s="11"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="14"/>
+      <c r="X41" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D42" s="11"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="14"/>
+      <c r="X42" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="11"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="14"/>
+      <c r="X43" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="11"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="14"/>
+      <c r="X44" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D45" s="11"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="14"/>
+      <c r="X45" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D46" s="11"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="14"/>
+      <c r="X46" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D47" s="11"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="14"/>
+      <c r="X47" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D48" s="11"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="14"/>
+      <c r="X48" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D49" s="11"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="14"/>
+      <c r="X49" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D50" s="11"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="14"/>
+      <c r="X50" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D51" s="11"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="14"/>
+      <c r="X51" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D52" s="11"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="10"/>
+      <c r="X52" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:25" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="22"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3">
+        <f>SUM(G3:G52)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="3">
+        <f t="shared" ref="H53:I53" si="3">SUM(H3:H52)</f>
+        <v>0.04</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -4283,11 +5783,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF92D050"/>
-  </sheetPr>
   <dimension ref="A1:Z53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4310,36 +5807,40 @@
       <c r="A1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="D1" s="32" t="s">
+      <c r="B1" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="33"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="33"/>
-      <c r="I1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="34"/>
+      <c r="I1" s="35"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="34"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="33"/>
-      <c r="Z1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="35"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="6"/>
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="D2" s="12" t="s">
         <v>31</v>
       </c>
@@ -4394,8 +5895,12 @@
       <c r="A3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="D3" s="11"/>
+      <c r="B3" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="11">
+        <v>46274</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="19" t="str">
         <f>IF(E3&gt;0,E3-D3,"")</f>
@@ -4417,30 +5922,30 @@
         <f>I53</f>
         <v>0</v>
       </c>
-      <c r="N3" s="7" t="e">
+      <c r="N3" s="7" t="str">
         <f>IF(B16=K3,XIRR(Y3:Y52,X3:X52),"")</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="O3" s="6">
+        <v/>
+      </c>
+      <c r="O3" s="6" t="str">
         <f>IF(B16=K3,MAX(E:E),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P3" s="2" t="str">
         <f ca="1">IF(Z3="+",TODAY()-B11,"")</f>
         <v/>
       </c>
-      <c r="Q3" s="2">
+      <c r="Q3" s="2" t="str">
         <f>IF(B16=K3,MAX(E:E)-B11,"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T3" s="13"/>
       <c r="X3" s="6">
         <f>B9</f>
-        <v>0</v>
+        <v>46251</v>
       </c>
       <c r="Y3" s="3">
         <f>B16*-1</f>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="Z3" s="2" t="str">
         <f ca="1">IF(AND(TODAY()&gt;B11, K3&lt;&gt;B16), "+", "")</f>
@@ -4451,8 +5956,12 @@
       <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="D4" s="11"/>
+      <c r="B4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="11">
+        <v>46304</v>
+      </c>
       <c r="E4" s="6"/>
       <c r="F4" s="19" t="str">
         <f>IF(E4&gt;0,E4-D4,"")</f>
@@ -4474,7 +5983,9 @@
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
-      <c r="D5" s="11"/>
+      <c r="D5" s="11">
+        <v>46335</v>
+      </c>
       <c r="E5" s="6"/>
       <c r="F5" s="19" t="str">
         <f t="shared" ref="F5:F52" si="0">IF(E5&gt;0,E5-D5,"")</f>
@@ -4496,7 +6007,9 @@
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
-      <c r="D6" s="11"/>
+      <c r="D6" s="11">
+        <v>46365</v>
+      </c>
       <c r="E6" s="6"/>
       <c r="F6" s="19" t="str">
         <f t="shared" si="0"/>
@@ -4518,7 +6031,9 @@
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
-      <c r="D7" s="11"/>
+      <c r="D7" s="11">
+        <v>46396</v>
+      </c>
       <c r="E7" s="6"/>
       <c r="F7" s="19" t="str">
         <f t="shared" si="0"/>
@@ -4543,9 +6058,11 @@
       </c>
       <c r="B8" s="6" t="str">
         <f>DATEDIF(B9,B11,"y") &amp; " m. " &amp; DATEDIF(B9,B11,"ym") &amp; " mėn. " &amp; DATEDIF(B9,B11,"md") &amp; " d."</f>
-        <v>0 m. 0 mėn. 0 d.</v>
-      </c>
-      <c r="D8" s="11"/>
+        <v>0 m. 11 mėn. 23 d.</v>
+      </c>
+      <c r="D8" s="11">
+        <v>46427</v>
+      </c>
       <c r="E8" s="6"/>
       <c r="F8" s="19" t="str">
         <f t="shared" si="0"/>
@@ -4568,8 +6085,12 @@
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="D9" s="11"/>
+      <c r="B9" s="6">
+        <v>46251</v>
+      </c>
+      <c r="D9" s="11">
+        <v>46455</v>
+      </c>
       <c r="E9" s="6"/>
       <c r="F9" s="19" t="str">
         <f t="shared" si="0"/>
@@ -4592,8 +6113,12 @@
       <c r="A10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="D10" s="11"/>
+      <c r="B10" s="6">
+        <v>46244</v>
+      </c>
+      <c r="D10" s="11">
+        <v>46486</v>
+      </c>
       <c r="E10" s="6"/>
       <c r="F10" s="19" t="str">
         <f t="shared" si="0"/>
@@ -4616,8 +6141,12 @@
       <c r="A11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="D11" s="11"/>
+      <c r="B11" s="6">
+        <v>46608</v>
+      </c>
+      <c r="D11" s="11">
+        <v>46516</v>
+      </c>
       <c r="E11" s="6"/>
       <c r="F11" s="19" t="str">
         <f t="shared" si="0"/>
@@ -4640,11 +6169,13 @@
       <c r="A12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="19" t="str">
+      <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v/>
-      </c>
-      <c r="D12" s="11"/>
+        <v>342</v>
+      </c>
+      <c r="D12" s="11">
+        <v>46547</v>
+      </c>
       <c r="E12" s="6"/>
       <c r="F12" s="19" t="str">
         <f t="shared" si="0"/>
@@ -4666,7 +6197,9 @@
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="3"/>
-      <c r="D13" s="11"/>
+      <c r="D13" s="11">
+        <v>46577</v>
+      </c>
       <c r="E13" s="6"/>
       <c r="F13" s="19" t="str">
         <f t="shared" si="0"/>
@@ -4689,7 +6222,9 @@
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="18"/>
-      <c r="D14" s="11"/>
+      <c r="D14" s="11">
+        <v>46608</v>
+      </c>
       <c r="E14" s="6"/>
       <c r="F14" s="19" t="str">
         <f t="shared" si="0"/>
@@ -4712,7 +6247,9 @@
       <c r="A15" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="7"/>
+      <c r="B15" s="7">
+        <v>0.12</v>
+      </c>
       <c r="D15" s="11"/>
       <c r="E15" s="6"/>
       <c r="F15" s="19" t="str">
@@ -4743,7 +6280,9 @@
       <c r="A16" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="3"/>
+      <c r="B16" s="3">
+        <v>10</v>
+      </c>
       <c r="D16" s="11"/>
       <c r="E16" s="6"/>
       <c r="F16" s="19" t="str">
